--- a/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente</t>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,19; 96,93</t>
+          <t>72,72; 96,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,91; 96,53</t>
+          <t>76,19; 96,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,21; 95,52</t>
+          <t>81,27; 95,58</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,63; 94,85</t>
+          <t>79,94; 94,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,91; 96,94</t>
+          <t>85,37; 96,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,87; 94,7</t>
+          <t>85,46; 94,51</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,77; 91,57</t>
+          <t>65,71; 91,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,56; 96,71</t>
+          <t>83,43; 97,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,35; 92,98</t>
+          <t>78,66; 92,98</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,29; 91,87</t>
+          <t>77,46; 91,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,98; 91,99</t>
+          <t>77,3; 91,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,94; 90,42</t>
+          <t>79,72; 90,12</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,27; 90,39</t>
+          <t>80,42; 90,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,12; 92,46</t>
+          <t>85,06; 92,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,0</t>
+          <t>85,05; 90,96</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20950</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36112</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>12463; 16590</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17635; 22372</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32740; 38506</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>44303</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58234</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>102536</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>39880; 47332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53489; 60728</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96180; 106359</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>47332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54521</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>101853</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>37355; 52183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49345; 57412</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>91243; 107855</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>61451</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141381</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>55500; 65806</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>71895; 85280</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131265; 148394</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>168247</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>213635</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>381882</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>157227; 176039</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202410; 220819</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368685; 394305</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,72; 96,8</t>
+          <t>73,05; 96,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,19; 96,65</t>
+          <t>78,34; 97,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,27; 95,58</t>
+          <t>80,09; 95,23</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,94; 94,88</t>
+          <t>79,25; 94,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,37; 96,92</t>
+          <t>86,0; 96,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,46; 94,51</t>
+          <t>85,55; 94,86</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,71; 91,8</t>
+          <t>64,91; 91,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,43; 97,06</t>
+          <t>83,31; 96,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,66; 92,98</t>
+          <t>78,98; 92,94</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,46; 91,85</t>
+          <t>77,31; 91,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,3; 91,69</t>
+          <t>77,06; 91,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,72; 90,12</t>
+          <t>79,85; 90,48</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,42; 90,04</t>
+          <t>80,54; 90,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,06; 92,8</t>
+          <t>85,13; 92,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,05; 90,96</t>
+          <t>85,07; 90,66</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12463; 16590</t>
+          <t>12519; 16598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17635; 22372</t>
+          <t>18133; 22559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32740; 38506</t>
+          <t>32265; 38363</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39880; 47332</t>
+          <t>39534; 47357</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53489; 60728</t>
+          <t>53887; 60728</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96180; 106359</t>
+          <t>96277; 106756</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37355; 52183</t>
+          <t>36902; 52079</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49345; 57412</t>
+          <t>49277; 57317</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91243; 107855</t>
+          <t>91608; 107801</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55500; 65806</t>
+          <t>55389; 65631</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71895; 85280</t>
+          <t>71673; 85526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131265; 148394</t>
+          <t>131483; 148982</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>157227; 176039</t>
+          <t>157476; 176004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202410; 220819</t>
+          <t>202587; 220907</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368685; 394305</t>
+          <t>368776; 392975</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,05; 96,85</t>
+          <t>70,46; 96,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,34; 97,45</t>
+          <t>75,4; 97,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,09; 95,23</t>
+          <t>79,56; 95,13</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 94,93</t>
+          <t>85,55; 97,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,0; 96,92</t>
+          <t>77,65; 94,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,55; 94,86</t>
+          <t>84,44; 94,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,91; 91,61</t>
+          <t>82,92; 96,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,31; 96,9</t>
+          <t>76,77; 92,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,98; 92,94</t>
+          <t>82,89; 93,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,31; 91,6</t>
+          <t>77,38; 92,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,06; 91,95</t>
+          <t>76,93; 92,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,85; 90,48</t>
+          <t>80,22; 90,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,54; 90,02</t>
+          <t>84,72; 92,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,13; 92,83</t>
+          <t>82,0; 90,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,07; 90,66</t>
+          <t>85,25; 91,16</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36112</t>
+          <t>30392</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12519; 16598</t>
+          <t>13367; 18296</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18133; 22559</t>
+          <t>11534; 14868</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32265; 38363</t>
+          <t>27265; 32599</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>44303</t>
+          <t>50163</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58234</t>
+          <t>38745</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102536</t>
+          <t>88908</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39534; 47357</t>
+          <t>46116; 52287</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53887; 60728</t>
+          <t>34392; 41711</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96277; 106756</t>
+          <t>82918; 92639</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101853</t>
+          <t>100849</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36902; 52079</t>
+          <t>46516; 54192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49277; 57317</t>
+          <t>43622; 52829</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91608; 107801</t>
+          <t>93601; 106066</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>61451</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79930</t>
+          <t>65321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141381</t>
+          <t>144536</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55389; 65631</t>
+          <t>71045; 84578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71673; 85526</t>
+          <t>58564; 70060</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131483; 148982</t>
+          <t>134714; 152105</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>247</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>168247</t>
+          <t>197686</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>157476; 176004</t>
+          <t>187060; 203898</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202587; 220907</t>
+          <t>157881; 174815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368776; 392975</t>
+          <t>352379; 376801</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>88,38%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>70,46; 96,44</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>75,4; 97,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79,56; 95,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>85,55; 97,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>77,65; 94,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>84,44; 94,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>82,92; 96,6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>76,77; 92,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>82,89; 93,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>86,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>77,38; 92,12</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>76,93; 92,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80,22; 90,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>84,72; 92,35</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>82,0; 90,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>85,25; 91,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8838345862834547</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8905983754363253</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8868539412628608</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16768</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13624</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30392</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7045900268101086</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.7539675048905813</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7956068290229166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13367; 18296</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11534; 14868</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27265; 32599</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9643514079126551</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9718826031536976</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9512655433454347</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9305821844667497</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8747404814370883</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9053945006919123</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>50163</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>38745</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88908</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8555075698825593</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.776458176214973</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8443994433949701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>46116; 52287</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34392; 41711</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>82918; 92639</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9699872627893236</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9417150066945061</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9433911658592837</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.918770455066755</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8677222171823519</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8930820409180793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49307</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>100849</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8292067931042405</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7676724096541693</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8288992511139455</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>46516; 54192</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43622; 52829</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>93601; 106066</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9660374887873507</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9296898366311132</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9392886166216505</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.862791059532677</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8580577736108054</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8606454584422936</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>79215</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>65321</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>144536</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7738125385904233</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7692894276780325</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8021627155158196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>71045; 84578</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>58564; 70060</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>134714; 152105</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9212111567093262</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9203066522319738</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.905713382065461</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8953737853545477</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8673331533679137</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8823115464351646</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>197686</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>166998</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>364684</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8472461812517955</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8199807980237833</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.852541473976632</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>187060; 203898</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>157881; 174815</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>352379; 376801</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9235097441168798</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.90793306823441</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9116282177273293</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>16768</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>13624</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>30392</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>13367</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>11534</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>27265</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>18296</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>14868</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>32599</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>50163</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>38745</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>88908</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>34392</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>82918</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>52287</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>41711</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>92639</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>51540</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>49307</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>100849</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>46516</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>43622</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>93601</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>54192</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>52829</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>106066</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>79215</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>65321</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>144536</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>71045</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>58564</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>134714</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>84578</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>70060</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>152105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>197686</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>166998</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>364684</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>187060</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>157881</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>352379</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>203898</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>174815</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>376801</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>